--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488297_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488297_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3428</v>
+        <v>10.2188</v>
       </c>
       <c r="E2" t="n">
-        <v>9.521100000000001</v>
+        <v>10.077</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1783</v>
+        <v>0.1418</v>
       </c>
       <c r="G2" t="n">
         <v>8.6798</v>
@@ -610,13 +610,13 @@
         <v>2.9646</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.0225</v>
+        <v>-1.1465</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2709</v>
+        <v>-0.715</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7516</v>
+        <v>-0.4315</v>
       </c>
       <c r="V2" t="n">
         <v>1.5738</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>A. VICENTE FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9275</v>
+        <v>0.5406</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1729</v>
+        <v>-1.7502</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1004</v>
+        <v>2.2908</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7153</v>
+        <v>-1.0417</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7637</v>
+        <v>0.4898</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.479</v>
+        <v>-1.5316</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5018</v>
+        <v>-0.7378</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9058</v>
+        <v>1.1165</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.404</v>
+        <v>-1.8543</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2171</v>
+        <v>-0.304</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1421</v>
+        <v>-0.6267</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.075</v>
+        <v>0.3227</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4823</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4087</v>
+        <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0.476</v>
+        <v>-0.6771</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0621</v>
+        <v>-0.4184</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5382</v>
+        <v>-0.2587</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3155</v>
+        <v>1.8888</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3139</v>
+        <v>1.2589</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6294</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. VICENTE FERNANDEZ</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5476</v>
+        <v>0.2332</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.7185</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2662</v>
+        <v>0.8295</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0417</v>
+        <v>-0.7153</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4898</v>
+        <v>0.7637</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5316</v>
+        <v>-1.479</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7378</v>
+        <v>0.5018</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1165</v>
+        <v>0.9058</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8543</v>
+        <v>-0.404</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.304</v>
+        <v>-1.2171</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6267</v>
+        <v>-0.1421</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3227</v>
+        <v>-1.075</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>1.4823</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2234</v>
+        <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.67</v>
+        <v>-0.2182</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3867</v>
+        <v>-0.4856</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2833</v>
+        <v>0.2673</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8888</v>
+        <v>-0.3155</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2589</v>
+        <v>0.3139</v>
       </c>
       <c r="X6" t="n">
-        <v>0.63</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. VIDAL</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0722</v>
+        <v>-0.0146</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1262</v>
+        <v>-1.0679</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1984</v>
+        <v>1.0533</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9349</v>
+        <v>-0.0495</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2434</v>
+        <v>0.9105</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3084</v>
+        <v>-0.96</v>
       </c>
       <c r="J7" t="n">
-        <v>3.083</v>
+        <v>0.0342</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8342</v>
+        <v>0.6871</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2488</v>
+        <v>-0.6529</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1481</v>
+        <v>-0.0837</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4092</v>
+        <v>0.2234</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.5573</v>
+        <v>-0.3071</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.594</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.6322</v>
+        <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0382</v>
+        <v>0.7411</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6419</v>
+        <v>-0.0948</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4726</v>
+        <v>-0.1756</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1693</v>
+        <v>0.0808</v>
       </c>
       <c r="V7" t="n">
-        <v>0.945</v>
+        <v>0.315</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2578</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3396</v>
+        <v>-0.1691</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2205</v>
+        <v>0.3937</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8809</v>
+        <v>-0.5628</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0495</v>
+        <v>1.6065</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9105</v>
+        <v>-0.9877</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.96</v>
+        <v>2.5942</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0342</v>
+        <v>2.9165</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6871</v>
+        <v>-1.0138</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6529</v>
+        <v>3.9303</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0837</v>
+        <v>-1.31</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2234</v>
+        <v>0.0262</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3071</v>
+        <v>-1.3361</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7411</v>
+        <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4198</v>
+        <v>-0.7583</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3283</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0915</v>
+        <v>-0.0883</v>
       </c>
       <c r="V8" t="n">
-        <v>0.315</v>
+        <v>-1.5733</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.315</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>B. VIDAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4493</v>
+        <v>-0.6488</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0095</v>
+        <v>0.648</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4397</v>
+        <v>-1.2968</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6065</v>
+        <v>0.9349</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9877</v>
+        <v>3.2434</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5942</v>
+        <v>-2.3084</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9165</v>
+        <v>3.083</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0138</v>
+        <v>2.8342</v>
       </c>
       <c r="L9" t="n">
-        <v>3.9303</v>
+        <v>0.2488</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.31</v>
+        <v>-2.1481</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0262</v>
+        <v>0.4092</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3361</v>
+        <v>-2.5573</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.594</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8529</v>
+        <v>-4.6322</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4087</v>
+        <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0384</v>
+        <v>0.0653</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0732</v>
+        <v>-0.0056</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0348</v>
+        <v>0.0709</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5733</v>
+        <v>0.945</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>-1.2578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4679</v>
+        <v>-1.1867</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8979</v>
+        <v>-1.6905</v>
       </c>
       <c r="F10" t="n">
-        <v>0.43</v>
+        <v>0.5038</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7563</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3972</v>
+        <v>-0.116</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.383</v>
+        <v>-0.1756</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0142</v>
+        <v>0.0597</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3144</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7806</v>
+        <v>-4.4507</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3976</v>
+        <v>-4.0923</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.383</v>
+        <v>-0.3584</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4044</v>
@@ -1312,13 +1312,13 @@
         <v>2.0382</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0617</v>
+        <v>-0.7318</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.909</v>
+        <v>-0.6037</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1527</v>
+        <v>-0.1281</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5733</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7087</v>
+        <v>-5.7536</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6189</v>
+        <v>-4.3683</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0898</v>
+        <v>-1.3852</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8316</v>
@@ -1390,13 +1390,13 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1174</v>
+        <v>-0.1623</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5596</v>
+        <v>-0.309</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4422</v>
+        <v>0.1467</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5744</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4774</v>
+        <v>-6.1524</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2503</v>
+        <v>-4.0976</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2271</v>
+        <v>-2.0547</v>
       </c>
       <c r="G13" t="n">
         <v>-4.8962</v>
@@ -1468,13 +1468,13 @@
         <v>1.1117</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5081</v>
+        <v>-0.1831</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2313</v>
+        <v>-0.0786</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2768</v>
+        <v>-0.1045</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2583</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.245399999999999</v>
+        <v>-5.1509</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.4064</v>
+        <v>-4.312000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8387999999999998</v>
+        <v>-0.8387</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7585999999999977</v>
+        <v>0.7585999999999995</v>
       </c>
       <c r="H14" t="n">
         <v>9.052700000000002</v>
@@ -1525,7 +1525,7 @@
         <v>10.3728</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7634</v>
+        <v>2.763399999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-12.3776</v>
@@ -1537,7 +1537,7 @@
         <v>-11.0577</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0001000000000001</v>
+        <v>9.999999999987796e-05</v>
       </c>
       <c r="Q14" t="n">
         <v>-18.5287</v>
@@ -1546,13 +1546,13 @@
         <v>18.5286</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.1172</v>
+        <v>-4.0228</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.7315</v>
+        <v>-3.637</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3855999999999999</v>
+        <v>-0.3856999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8866</v>
@@ -1561,13 +1561,13 @@
         <v>4.7177</v>
       </c>
       <c r="X14" t="n">
-        <v>-6.604299999999999</v>
+        <v>-6.6043</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.243</v>
+        <v>5.3156</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8854</v>
+        <v>3.9049</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3576</v>
+        <v>1.4107</v>
       </c>
       <c r="G15" t="n">
-        <v>1.107</v>
+        <v>6.3353</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2663</v>
+        <v>-0.6963</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3733</v>
+        <v>7.0316</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3747</v>
+        <v>8.2958</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4717</v>
+        <v>1.1722</v>
       </c>
       <c r="L15" t="n">
-        <v>2.903</v>
+        <v>7.1236</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2677</v>
+        <v>-1.9605</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.738</v>
+        <v>-1.8685</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.092</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9264</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7057</v>
+        <v>-4.6322</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7793</v>
+        <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2853</v>
+        <v>0.3895</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7549</v>
+        <v>-0.3876</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5305</v>
+        <v>0.7772</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7771</v>
+        <v>0.6289</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4616</v>
+        <v>0.6289</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5734</v>
+        <v>4.8673</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2194</v>
+        <v>3.2978</v>
       </c>
       <c r="F16" t="n">
-        <v>1.354</v>
+        <v>1.5695</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3353</v>
+        <v>1.107</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6963</v>
+        <v>-1.2663</v>
       </c>
       <c r="I16" t="n">
-        <v>7.0316</v>
+        <v>2.3733</v>
       </c>
       <c r="J16" t="n">
-        <v>8.2958</v>
+        <v>3.3747</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1722</v>
+        <v>0.4717</v>
       </c>
       <c r="L16" t="n">
-        <v>7.1236</v>
+        <v>2.903</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9605</v>
+        <v>-2.2677</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8685</v>
+        <v>-1.738</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.092</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0382</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.6322</v>
+        <v>-3.7057</v>
       </c>
       <c r="R16" t="n">
-        <v>2.594</v>
+        <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3527</v>
+        <v>0.9096</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0732</v>
+        <v>0.1673</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7205</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6289</v>
+        <v>3.7771</v>
       </c>
       <c r="W16" t="n">
-        <v>0.6289</v>
+        <v>3.4616</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3328</v>
+        <v>3.2794</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3456</v>
+        <v>2.0311</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9872</v>
+        <v>1.2483</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3665</v>
@@ -1780,13 +1780,13 @@
         <v>2.9646</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0211</v>
+        <v>0.9255</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8244</v>
+        <v>-0.1389</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8033</v>
+        <v>1.0644</v>
       </c>
       <c r="V17" t="n">
         <v>3.4616</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5239</v>
+        <v>1.3767</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4615</v>
+        <v>0.3636</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0623</v>
+        <v>1.0131</v>
       </c>
       <c r="G18" t="n">
         <v>1.4056</v>
@@ -1858,13 +1858,13 @@
         <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6747</v>
+        <v>0.5276</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1816</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4932</v>
+        <v>0.4439</v>
       </c>
       <c r="V18" t="n">
         <v>-0.0005</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5597</v>
+        <v>0.4663</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0118</v>
+        <v>-2.4554</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.452</v>
+        <v>2.9217</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3744</v>
+        <v>-1.2899</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.1502</v>
+        <v>-1.4328</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2242</v>
+        <v>0.1429</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1707</v>
+        <v>-2.0591</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2536</v>
+        <v>-1.5721</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0829</v>
+        <v>-0.487</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2037</v>
+        <v>0.7692</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8966</v>
+        <v>0.1393</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3071</v>
+        <v>0.6299</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3221</v>
+        <v>0.0886</v>
       </c>
       <c r="T22" t="n">
-        <v>0.868</v>
+        <v>-0.3964</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4541</v>
+        <v>0.485</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1304</v>
+        <v>0.1927</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7492</v>
+        <v>0.62</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6188</v>
+        <v>-0.4274</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2899</v>
+        <v>-1.3744</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.4328</v>
+        <v>-1.1502</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1429</v>
+        <v>-0.2242</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0591</v>
+        <v>-0.1707</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5721</v>
+        <v>-0.2536</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.487</v>
+        <v>0.0829</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7692</v>
+        <v>-1.2037</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1393</v>
+        <v>-0.8966</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6299</v>
+        <v>-0.3071</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5081</v>
+        <v>0.955</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6901</v>
+        <v>0.4763</v>
       </c>
       <c r="U24" t="n">
-        <v>0.182</v>
+        <v>0.4788</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7528</v>
+        <v>-0.8164</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4835</v>
+        <v>-0.9732</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2693</v>
+        <v>0.1568</v>
       </c>
       <c r="G25" t="n">
         <v>-2.5065</v>
@@ -2404,13 +2404,13 @@
         <v>2.2234</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1597</v>
+        <v>0.0961</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5061</v>
+        <v>0.0165</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3465</v>
+        <v>0.0796</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6294</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.5347</v>
+        <v>-1.3389</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.0906</v>
+        <v>-0.8947000000000001</v>
       </c>
       <c r="F26" t="n">
         <v>-0.4441</v>
@@ -2482,10 +2482,10 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1094</v>
+        <v>0.0864</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1641</v>
+        <v>0.0317</v>
       </c>
       <c r="U26" t="n">
         <v>0.0547</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.3922</v>
+        <v>-3.4987</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.1288</v>
+        <v>-2.4225</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2635</v>
+        <v>-1.0762</v>
       </c>
       <c r="G27" t="n">
         <v>-3.397</v>
@@ -2560,13 +2560,13 @@
         <v>2.594</v>
       </c>
       <c r="S27" t="n">
-        <v>0.856</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2661</v>
+        <v>-0.0276</v>
       </c>
       <c r="U27" t="n">
-        <v>0.5899</v>
+        <v>0.7772</v>
       </c>
       <c r="V27" t="n">
         <v>-2.5188</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-4.9878</v>
+        <v>-5.1034</v>
       </c>
       <c r="E28" t="n">
         <v>-5.4431</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4553</v>
+        <v>0.3397</v>
       </c>
       <c r="G28" t="n">
         <v>-2.9836</v>
@@ -2638,13 +2638,13 @@
         <v>1.4823</v>
       </c>
       <c r="S28" t="n">
-        <v>1.8106</v>
+        <v>1.6949</v>
       </c>
       <c r="T28" t="n">
         <v>0.5609</v>
       </c>
       <c r="U28" t="n">
-        <v>1.2497</v>
+        <v>1.1341</v>
       </c>
       <c r="V28" t="n">
         <v>-2.5177</v>
@@ -2671,22 +2671,22 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>6.245299999999997</v>
+        <v>7.550999999999999</v>
       </c>
       <c r="E29" t="n">
         <v>0.8388999999999998</v>
       </c>
       <c r="F29" t="n">
-        <v>5.406299999999999</v>
+        <v>6.712099999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7584999999999966</v>
+        <v>-0.7584999999999984</v>
       </c>
       <c r="H29" t="n">
         <v>-9.0527</v>
       </c>
       <c r="I29" t="n">
-        <v>8.294399999999996</v>
+        <v>8.2944</v>
       </c>
       <c r="J29" t="n">
         <v>12.3776</v>
@@ -2707,7 +2707,7 @@
         <v>-2.7633</v>
       </c>
       <c r="P29" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>6.661338147750939e-16</v>
       </c>
       <c r="Q29" t="n">
         <v>-18.5286</v>
@@ -2716,13 +2716,13 @@
         <v>18.5286</v>
       </c>
       <c r="S29" t="n">
-        <v>5.1171</v>
+        <v>6.422700000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3857999999999999</v>
+        <v>0.3858</v>
       </c>
       <c r="U29" t="n">
-        <v>4.7314</v>
+        <v>6.0373</v>
       </c>
       <c r="V29" t="n">
         <v>1.886799999999999</v>
